--- a/docs/yardi-employee-receivables/CPR-EMPRCV-2026-001.xlsx
+++ b/docs/yardi-employee-receivables/CPR-EMPRCV-2026-001.xlsx
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="B22" s="24">
-        <f>B20*B21</f>
+        <f>IF(B20="","",B20*B21)</f>
         <v/>
       </c>
       <c r="C22" s="16" t="inlineStr">
